--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93217</v>
+        <v>93220</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93220</v>
+        <v>93221</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93221</v>
+        <v>93226</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93226</v>
+        <v>93228</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93228</v>
+        <v>93230</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93230</v>
+        <v>93232</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93232</v>
+        <v>93233</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93233</v>
+        <v>93239</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93239</v>
+        <v>93243</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93243</v>
+        <v>93245</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93245</v>
+        <v>93258</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93258</v>
+        <v>93260</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93260</v>
+        <v>93263</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93263</v>
+        <v>93273</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93273</v>
+        <v>93274</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93274</v>
+        <v>93278</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93278</v>
+        <v>93280</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>

--- a/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
+++ b/artfynd/Muorkenåive-Ássjátj N artfynd.xlsx
@@ -29882,7 +29882,7 @@
         <v>135383916</v>
       </c>
       <c r="B253" t="n">
-        <v>93280</v>
+        <v>93286</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
